--- a/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/DuomenysTestui/zive_irasai_testui_updated.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/DuomenysTestui/zive_irasai_testui_updated.xlsx
@@ -780,16 +780,16 @@
         <v>0</v>
       </c>
       <c r="T2" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V2" s="8" t="n">
         <v>3</v>
       </c>
       <c r="W2" s="9" t="n">
-        <v>0.5</v>
+        <v>17.2</v>
       </c>
       <c r="X2" s="8" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="T3" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V3" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W3" s="9" t="n">
-        <v>0.5</v>
+        <v>86.7</v>
       </c>
       <c r="X3" s="8" t="n">
         <v>0</v>
@@ -996,16 +996,16 @@
         <v>0</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W4" s="9" t="n">
-        <v>0.5</v>
+        <v>54.4</v>
       </c>
       <c r="X4" s="8" t="n">
         <v>0</v>
@@ -1106,16 +1106,16 @@
         <v>6.5</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W5" s="9" t="n">
-        <v>0.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="X5" s="8" t="n">
         <v>0</v>
@@ -1214,16 +1214,16 @@
         <v>2.4</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>0.5</v>
+        <v>36.8</v>
       </c>
       <c r="X6" s="8" t="n">
         <v>0</v>
@@ -1322,13 +1322,13 @@
         <v>1</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W7" s="9" t="n">
-        <v>0.5</v>
+        <v>7.1</v>
       </c>
       <c r="X7" s="8" t="n">
         <v>0</v>
@@ -1422,16 +1422,16 @@
         <v>2</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W8" s="9" t="n">
-        <v>0.5</v>
+        <v>50.6</v>
       </c>
       <c r="X8" s="8" t="n">
         <v>0</v>
@@ -1530,16 +1530,16 @@
         <v>0.2</v>
       </c>
       <c r="T9" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X9" s="8" t="n">
         <v>0</v>
@@ -1628,16 +1628,16 @@
         <v>0</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W10" s="9" t="n">
-        <v>0.5</v>
+        <v>42.8</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>0</v>
@@ -1736,16 +1736,16 @@
         <v>0.5</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V11" s="8" t="n">
         <v>3</v>
       </c>
       <c r="W11" s="9" t="n">
-        <v>0.5</v>
+        <v>14.6</v>
       </c>
       <c r="X11" s="8" t="n">
         <v>0</v>
@@ -1836,16 +1836,16 @@
         <v>0</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V12" s="8" t="n">
         <v>3</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>0.5</v>
+        <v>14.3</v>
       </c>
       <c r="X12" s="8" t="n">
         <v>0</v>
@@ -1919,16 +1919,16 @@
         <v>2.6</v>
       </c>
       <c r="T13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="U13" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="W13" s="9" t="n">
-        <v>0.5</v>
+        <v>26.4</v>
       </c>
       <c r="X13" s="8" t="n">
         <v>0</v>
@@ -2008,16 +2008,16 @@
         <v>7.6</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" s="8" t="n">
         <v>3</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>0.5</v>
+        <v>41.2</v>
       </c>
       <c r="X14" s="8" t="n">
         <v>0</v>
